--- a/outils-mapping/ig/cm-v3-administrative-gender.xlsx
+++ b/outils-mapping/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T14:34:23+00:00</t>
+    <t>2026-03-27T15:11:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/outils-mapping/ig/cm-v3-administrative-gender.xlsx
+++ b/outils-mapping/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T15:11:52+00:00</t>
+    <t>2026-03-30T14:26:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/outils-mapping/ig/cm-v3-administrative-gender.xlsx
+++ b/outils-mapping/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T14:26:28+00:00</t>
+    <t>2026-03-30T14:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/outils-mapping/ig/cm-v3-administrative-gender.xlsx
+++ b/outils-mapping/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T14:27:13+00:00</t>
+    <t>2026-04-01T07:35:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/outils-mapping/ig/cm-v3-administrative-gender.xlsx
+++ b/outils-mapping/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:35:37+00:00</t>
+    <t>2026-04-01T07:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/outils-mapping/ig/cm-v3-administrative-gender.xlsx
+++ b/outils-mapping/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:55:26+00:00</t>
+    <t>2026-04-01T13:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/outils-mapping/ig/cm-v3-administrative-gender.xlsx
+++ b/outils-mapping/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T13:27:53+00:00</t>
+    <t>2026-04-01T13:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/outils-mapping/ig/cm-v3-administrative-gender.xlsx
+++ b/outils-mapping/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T13:32:02+00:00</t>
+    <t>2026-04-01T15:00:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/outils-mapping/ig/cm-v3-administrative-gender.xlsx
+++ b/outils-mapping/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T15:00:22+00:00</t>
+    <t>2026-04-01T15:02:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/outils-mapping/ig/cm-v3-administrative-gender.xlsx
+++ b/outils-mapping/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T15:02:35+00:00</t>
+    <t>2026-04-01T20:38:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/outils-mapping/ig/cm-v3-administrative-gender.xlsx
+++ b/outils-mapping/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T20:38:02+00:00</t>
+    <t>2026-04-01T20:39:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/outils-mapping/ig/cm-v3-administrative-gender.xlsx
+++ b/outils-mapping/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T20:39:05+00:00</t>
+    <t>2026-04-01T20:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/outils-mapping/ig/cm-v3-administrative-gender.xlsx
+++ b/outils-mapping/ig/cm-v3-administrative-gender.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T20:41:15+00:00</t>
+    <t>2026-04-02T09:31:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
